--- a/diseases/d248/2015-2019.xlsx
+++ b/diseases/d248/2015-2019.xlsx
@@ -768,9 +768,9 @@
       <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>missing_population</t>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -785,26 +785,16 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>HOLD_US_a1bb05668cb509d11c2247438015; HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -842,238 +832,6 @@
         </is>
       </c>
       <c r="BC2" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>D248</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>powassan-virus-disease</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>US-NY</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>New York, United States</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>D248</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>波瓦桑病毒病</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2019-12-14</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2019-12</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>HOLD_US_a1bb05668cb509d11c2247438015</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Arboviral diseases, neuroinvasive and non-neuroinvasive, Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Arboviral diseases, neuroinvasive and non-neuroinvasive, Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>country:US-NY:national</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>HOLD_US_a1bb05668cb509d11c2247438015; HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
-      <c r="AT3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -1205,7 +963,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1225,7 +983,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1235,7 +993,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
